--- a/backend/demo.xlsx
+++ b/backend/demo.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/backend/demo.xlsx
+++ b/backend/demo.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="watch_pool" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,16 +413,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,10 +454,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>颈到肩最小价差</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>交易时间段</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>监控开关</t>
         </is>
@@ -484,12 +490,15 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>day,night</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>开启</t>
         </is>
@@ -517,12 +526,15 @@
       <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>开启</t>
         </is>

--- a/backend/demo.xlsx
+++ b/backend/demo.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="watch_pool" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="watch_pool_demo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +54,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,128 +427,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>品种名称</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>监控品种</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>监控周期</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>检测时长</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>头部到颈线最小高度</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>颈到肩最小价差</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>头部到左颈，头部到右颈最小高度</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>左颈到左肩，右颈到右肩最小价差</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>启用关键区间趋势评分</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>阻挡区间</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>支撑区间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>交易时间段</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>监控开关</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>螺纹钢</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SHFE.rb2605</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>1m</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>day,night</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>开启</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>热卷</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SHFE.hc2610</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="C3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="D3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>开启</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>3500-3520</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>3300-3320</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>开启</t>
         </is>

--- a/backend/demo.xlsx
+++ b/backend/demo.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="watch_pool_demo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'watch_pool_demo'!$A$1:$I$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -27,6 +29,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -38,11 +41,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,17 +53,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -437,11 +454,11 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>监控品种</t>
@@ -505,10 +522,8 @@
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>关闭</t>
-        </is>
+      <c r="E2" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
@@ -517,10 +532,8 @@
           <t>day,night</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>开启</t>
-        </is>
+      <c r="I2" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -540,10 +553,8 @@
       <c r="D3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>开启</t>
-        </is>
+      <c r="E3" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -560,13 +571,90 @@
           <t>day</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>开启</t>
-        </is>
+      <c r="I3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CZCE.SA609</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1600-1620</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1500-1520</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DCE.m2609</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>day,night</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I5"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1m,3m,5m,15m,30m,60m,1h"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E200 I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE,1,0"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>